--- a/out/MLP-Mamba1_repeat_1_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003531936371456832</v>
+        <v>-0.0002556174543260131</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.152074818486476</v>
+        <v>0.1100614542579717</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3045556994270894</v>
+        <v>0.220416633438058</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5875454490769426</v>
+        <v>0.4252256041575488</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.099999930000001</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.327962116108503</v>
+        <v>0.9610878428122648</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1807327827582897</v>
+        <v>0.1308017795310258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.101136792740634</v>
+        <v>0.7969274979848575</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0366718194647762</v>
+        <v>0.02654065405533219</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.499999930000002</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9934653235341842</v>
+        <v>0.7190023996632446</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03175942545803098</v>
+        <v>0.02298502816703271</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.020272116697352</v>
+        <v>0.7384031773793388</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01552681214422354</v>
+        <v>0.0112372084466643</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.499999930000002</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.019524632240029</v>
+        <v>0.7378622009973514</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007409032196845492</v>
+        <v>0.005360418037190818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.018796516136101</v>
+        <v>0.7373338614061838</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00308362820646964</v>
+        <v>0.002230191465208292</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.499999930000002</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.017546228399768</v>
+        <v>0.7364275547385148</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002135616713332462</v>
+        <v>0.001544516351972453</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.018731037023608</v>
+        <v>0.7372838149103499</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008886261018224848</v>
+        <v>0.0006418641717590301</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.018370345519469</v>
+        <v>0.737021342473324</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004580429264972897</v>
+        <v>0.0003304221487758145</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.018397542819257</v>
+        <v>0.7370396484473862</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001771278379982307</v>
+        <v>0.0001267408856990083</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.018292541739904</v>
+        <v>0.7369623133726958</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.406555421110877e-05</v>
+        <v>6.657915766698612e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.018303915160177</v>
+        <v>0.7369691571484726</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.412644070038033e-05</v>
+        <v>3.057431912786162e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.018297417179956</v>
+        <v>0.7369630724041744</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.791150147070719e-05</v>
+        <v>1.151759408353309e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.018289590017412</v>
+        <v>0.7369560253192582</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.145780771925869e-06</v>
+        <v>2.378749652309724e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.018281408128245</v>
+        <v>0.7369487112180461</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.018275343907207</v>
+        <v>0.7369429372391091</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.018269286825489</v>
+        <v>0.7369371680962415</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.018263471323336</v>
+        <v>0.7369316244281391</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.018258590025086</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.018253668823539</v>
+        <v>0.7369267431298899</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.018253660852444</v>
+        <v>0.7369267351587955</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.018253820274333</v>
+        <v>0.7369268945806846</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.018254075349356</v>
+        <v>0.7369271496557074</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.018253788389955</v>
+        <v>0.7369268626963068</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.099999930000001</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.099999930000001</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.018253923898561</v>
+        <v>0.7369269982049128</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.018253860129805</v>
+        <v>0.7369269344361569</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.018253820274333</v>
+        <v>0.7369268945806846</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.018253549257122</v>
+        <v>0.7369266235634732</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.018253469546177</v>
+        <v>0.7369265438525283</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.018253517372744</v>
+        <v>0.736926591679095</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.018253636939161</v>
+        <v>0.7369267112455121</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.018253620996972</v>
+        <v>0.7369266953033232</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.018253636939161</v>
+        <v>0.7369267112455121</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.018253620996972</v>
+        <v>0.7369266953033232</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.018253676794633</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.018253676794633</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.099999930000001</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.018253676794633</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7369269025517791</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.018254043464978</v>
+        <v>0.7369271177713296</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.018253955782939</v>
+        <v>0.7369270300892906</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.018253907956372</v>
+        <v>0.7369269822627238</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.018253955782939</v>
+        <v>0.7369270300892906</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.018253772447766</v>
+        <v>0.7369268467541179</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.018253780418861</v>
+        <v>0.7369268547252124</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.018253788389955</v>
+        <v>0.7369268626963068</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7369268706674013</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.099999930000001</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.018253836216522</v>
+        <v>0.7369269105228735</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.018253899985278</v>
+        <v>0.7369269742916293</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.099999930000001</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.0182540115806</v>
+        <v>0.7369270858869518</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.018254059407167</v>
+        <v>0.7369271337135185</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.018254019551695</v>
+        <v>0.7369270938580462</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.499999930000002</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.018253947811845</v>
+        <v>0.7369270221181962</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.018254067378262</v>
+        <v>0.7369271416846129</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.018253907956372</v>
+        <v>0.7369269822627238</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.018253676794633</v>
+        <v>0.7369267511009844</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.018253660852444</v>
+        <v>0.7369267351587955</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.018253644910255</v>
+        <v>0.7369267192166066</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.018253525343838</v>
+        <v>0.7369265996501895</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.018253485488366</v>
+        <v>0.7369265597947172</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.018253764476672</v>
+        <v>0.7369268387830235</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.018253748534483</v>
+        <v>0.7369268228408346</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.018253684765728</v>
+        <v>0.7369267590720788</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.0182535811415</v>
+        <v>0.736926655447851</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.099999930000001</v>
+        <v>1.305315212968727</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.018253461575082</v>
+        <v>0.7369265358814339</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.0182535811415</v>
+        <v>0.736926655447851</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7369267032744177</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-1.520943964793116</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7369267989275511</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.9209439647931161</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.018253605054783</v>
+        <v>0.7369266793611343</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.905315212968727</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.018253613025877</v>
+        <v>0.7369266873322288</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.3199999880000002</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0003531936371456832</v>
+        <v>-0.0002698848497908329</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.152074818486476</v>
+        <v>0.1162045805068318</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.3045556994270894</v>
+        <v>0.2327192803155468</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5875454490769426</v>
+        <v>0.4489597496692456</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.327962116108503</v>
+        <v>1.014731364010902</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1807327827582897</v>
+        <v>0.1381020267254049</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC46" t="n">
-        <v>1.101136792740634</v>
+        <v>0.8414083417970033</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0366718194647762</v>
+        <v>0.02802213507960599</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.499999930000002</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.9934653235341842</v>
+        <v>0.7591335181733136</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.03175942545803098</v>
+        <v>0.02426805657534782</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.079999972000001</v>
       </c>
       <c r="JC48" t="n">
-        <v>1.020272116697352</v>
+        <v>0.7796172338845642</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01552681214422354</v>
+        <v>0.01186410208767117</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>2.499999930000002</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.019524632240029</v>
+        <v>0.7790460619427886</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.007409032196845492</v>
+        <v>0.005660427090577951</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.079999972000001</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.018796516136101</v>
+        <v>0.7784884933193926</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00308362820646964</v>
+        <v>0.002354894550689402</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.499999930000002</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.017546228399768</v>
+        <v>0.7775319082715975</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.002135616713332462</v>
+        <v>0.001630943558855379</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9999999825000003</v>
+        <v>1.079999972000001</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.018731037023608</v>
+        <v>0.7784362068593914</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0008886261018224848</v>
+        <v>0.000677944245084235</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>3.099999930000001</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.018370345519469</v>
+        <v>0.7781593734099416</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0004580429264972897</v>
+        <v>0.0003491309538868161</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.018397542819257</v>
+        <v>0.778178979318812</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001771278379982307</v>
+        <v>0.0001340889829093116</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.018292541739904</v>
+        <v>0.7780976096184417</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>9.406555421110877e-05</v>
+        <v>7.058759049633734e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.018303915160177</v>
+        <v>0.7781051139673737</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>4.412644070038033e-05</v>
+        <v>3.226833432442646e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.018297417179956</v>
+        <v>0.7780989695974907</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.791150147070719e-05</v>
+        <v>1.258324531472877e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.018289590017412</v>
+        <v>0.7780917924996368</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.145780771925869e-06</v>
+        <v>2.839921505579082e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.018281408128245</v>
+        <v>0.7780843337670986</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.525705377792857e-07</v>
+        <v>-1.69277857293039e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.018275343907207</v>
+        <v>0.7780785119615952</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.018269286825489</v>
+        <v>0.7780726471655939</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.452445000690905e-06</v>
+        <v>-4.634963333793937e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.018263471323336</v>
+        <v>0.7780669679888857</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.018258590025086</v>
+        <v>0.7780620866906364</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.018253668823539</v>
+        <v>0.7780571654890885</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.018253660852444</v>
+        <v>0.7780571575179941</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.018253820274333</v>
+        <v>0.7780573169398831</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.018254075349356</v>
+        <v>0.778057572014906</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7780573249109777</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.018253788389955</v>
+        <v>0.7780572850555053</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7780572930265998</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7780573249109777</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.018253923898561</v>
+        <v>0.7780574205641113</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.018253860129805</v>
+        <v>0.7780573567953555</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.3199999880000002</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.018253820274333</v>
+        <v>0.7780573169398831</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7780572930265998</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.018253549257122</v>
+        <v>0.7780570459226717</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.018253469546177</v>
+        <v>0.7780569662117269</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.018253517372744</v>
+        <v>0.7780570140382936</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.018253636939161</v>
+        <v>0.7780571336047107</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.018253620996972</v>
+        <v>0.7780571176625217</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.018253636939161</v>
+        <v>0.7780571336047107</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.018253620996972</v>
+        <v>0.7780571176625217</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.018253676794633</v>
+        <v>0.778057173460183</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.018253676794633</v>
+        <v>0.778057173460183</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.018253676794633</v>
+        <v>0.778057173460183</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3999999825000004</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.018253828245428</v>
+        <v>0.7780573249109777</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.018254043464978</v>
+        <v>0.7780575401305282</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.018253955782939</v>
+        <v>0.7780574524484891</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.3199999880000002</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.018253907956372</v>
+        <v>0.7780574046219224</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.018253955782939</v>
+        <v>0.7780574524484891</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.018253772447766</v>
+        <v>0.7780572691133164</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.018253780418861</v>
+        <v>0.7780572770844109</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.018253788389955</v>
+        <v>0.7780572850555053</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7780572930265998</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.01825379636105</v>
+        <v>0.7780572930265998</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.018253836216522</v>
+        <v>0.7780573328820721</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.099999930000001</v>
+        <v>2.079999952000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.018253899985278</v>
+        <v>0.778057396650828</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.099999930000001</v>
+        <v>1.279999972000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.0182540115806</v>
+        <v>0.7780575082461504</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.018254059407167</v>
+        <v>0.7780575560727171</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.018254019551695</v>
+        <v>0.7780575162172448</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.499999930000002</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.018253947811845</v>
+        <v>0.7780574444773947</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.2799999920000001</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.018254067378262</v>
+        <v>0.7780575640438115</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.018253907956372</v>
+        <v>0.7780574046219224</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.018253676794633</v>
+        <v>0.778057173460183</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7780571256336163</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.018253660852444</v>
+        <v>0.7780571575179941</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.018253644910255</v>
+        <v>0.7780571415758052</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.018253525343838</v>
+        <v>0.7780570220093881</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.018253485488366</v>
+        <v>0.7780569821539158</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7780571256336163</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.018253764476672</v>
+        <v>0.778057261142222</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.018253748534483</v>
+        <v>0.7780572452000331</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.018253684765728</v>
+        <v>0.7780571814312774</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9999999825000003</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.0182535811415</v>
+        <v>0.7780570778070495</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>3.099999930000001</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.018253461575082</v>
+        <v>0.7780569582406325</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3999999825000004</v>
+        <v>0.4799999920000002</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.0182535811415</v>
+        <v>0.7780570778070495</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3999999825000004</v>
+        <v>-0.3199999880000002</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.018253628968066</v>
+        <v>0.7780571256336163</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.3199999880000002</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.0182537246212</v>
+        <v>0.7780572212867497</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.018253605054783</v>
+        <v>0.7780571017203328</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.9999999825000003</v>
+        <v>-0.5199999880000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.018253613025877</v>
+        <v>0.7780571096914273</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4135846197605133</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.499123215675354</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.421576052904129</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3868837654590607</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4157521426677704</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4526275396347046</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4055034518241882</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4139690697193146</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4593856632709503</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3843877613544464</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4009477198123932</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3958321511745453</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4691215753555298</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.5048198103904724</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.279999972000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5361741185188293</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.079999952000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.508387565612793</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.279999972000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4242429733276367</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4437613487243652</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.3199999880000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4485739469528198</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3753485083580017</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3555789887905121</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3734716773033142</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3864521086215973</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4818181395530701</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4043160080909729</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3954553008079529</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3913592994213104</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3920240700244904</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4260509014129639</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4425262808799744</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4160672426223755</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3738590776920319</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4269236922264099</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3870893120765686</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4067479074001312</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4238965809345245</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4565865099430084</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4871770441532135</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.5994000434875488</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.279999972000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5621148347854614</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.079999952000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.734971821308136</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.079999952000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6635735034942627</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.079999952000001</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002698848497908329</v>
+        <v>-0.0001816752822221024</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1162045805068318</v>
+        <v>0.07822410178061202</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8435533046722412</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.079999952000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2327192803155468</v>
+        <v>0.1566569630070983</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4489597496692456</v>
+        <v>0.3022210742498265</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7457472085952759</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.279999972000001</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.014731364010902</v>
+        <v>0.6830750487817598</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1381020267254049</v>
+        <v>0.09296489660347235</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.208074077963829</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.279999972000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.8414083417970033</v>
+        <v>0.5664011813620098</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02802213507960599</v>
+        <v>0.01886306248949166</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6238056421279907</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.7591335181733136</v>
+        <v>0.5110173888417329</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02426805657534782</v>
+        <v>0.01633660823303623</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3940284252166748</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.079999972000001</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.7796172338845642</v>
+        <v>0.5248062758631562</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01186410208767117</v>
+        <v>0.007985702361668543</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.5558707714080811</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.7790460619427886</v>
+        <v>0.524420894243811</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.005660427090577951</v>
+        <v>0.003808255384588791</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4893820881843567</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.079999972000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.7784884933193926</v>
+        <v>0.5240439424238605</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002354894550689402</v>
+        <v>0.001583850919478074</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.552480936050415</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.16</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.7775319082715975</v>
+        <v>0.5233983419913631</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001630943558855379</v>
+        <v>0.001096175216267276</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4599079191684723</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.079999972000001</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.7784362068593914</v>
+        <v>0.5240054028804111</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000677944245084235</v>
+        <v>0.0004543766478726977</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5541836619377136</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.7781593734099416</v>
+        <v>0.5238174288811471</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003491309538868161</v>
+        <v>0.0002335372651652704</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.457836925983429</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.778178979318812</v>
+        <v>0.5238290030499527</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001340889829093116</v>
+        <v>8.842580738814138e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.476531445980072</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.7780976096184417</v>
+        <v>0.5237725621866074</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.058759049633734e-05</v>
+        <v>4.596436025889411e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4811369478702545</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7781051139673737</v>
+        <v>0.5237760087290115</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.226833432442646e-05</v>
+        <v>2.041022794847258e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.3382951617240906</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7780989695974907</v>
+        <v>0.5237702339116556</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.258324531472877e-05</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.4043991565704346</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7780917924996368</v>
+        <v>0.5237637718849604</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>2.839921505579082e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4001728892326355</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7780843337670986</v>
+        <v>0.5237571092005268</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.69277857293039e-06</v>
+        <v>-2.519583929697793e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4101686179637909</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7780785119615952</v>
+        <v>0.5237515287163241</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4045827686786652</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7780726471655939</v>
+        <v>0.5237459518591734</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4468304812908173</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.4799999920000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7780669679888857</v>
+        <v>0.5237405445165164</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.507382869720459</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7780620866906364</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4067879617214203</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.279999972000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7780571654890885</v>
+        <v>0.5237356632182673</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5549837946891785</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7780571575179941</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4364000856876373</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.279999972000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7780573169398831</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.6384798884391785</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4661517739295959</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.778057572014906</v>
+        <v>0.5237360697440847</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4287459254264832</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7780573249109777</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4971959292888641</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7780572850555053</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4362983107566833</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4070096909999847</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7780572930265998</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4068096876144409</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7116432785987854</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.279999972000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7780573249109777</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5126156806945801</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.279999972000001</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7780574205641113</v>
+        <v>0.52373591829329</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4196993708610535</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7780573567953555</v>
+        <v>0.5237358545245342</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3351714015007019</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7780573169398831</v>
+        <v>0.5237358146690619</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3848070502281189</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7780572930265998</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3713745474815369</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7780570459226717</v>
+        <v>0.5237355436518504</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3572162687778473</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7780569662117269</v>
+        <v>0.5237354639409056</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3893280923366547</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7780570140382936</v>
+        <v>0.5237355117674724</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.306883305311203</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7780571336047107</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4078851342201233</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7780571176625217</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3715525269508362</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7780571336047107</v>
+        <v>0.5237356313338895</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4424140751361847</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7780571176625217</v>
+        <v>0.5237356153917005</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3799578547477722</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.778057173460183</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3105915784835815</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.778057173460183</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.583121120929718</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.778057173460183</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3947193920612335</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.279999972000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7780573249109777</v>
+        <v>0.5237358226401564</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.5811317563056946</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.3</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7780575401305282</v>
+        <v>0.5237360378597069</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3693218529224396</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7780574524484891</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4434890151023865</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7780574046219224</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3670641183853149</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7780574524484891</v>
+        <v>0.5237359501776679</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3490746915340424</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7780572691133164</v>
+        <v>0.5237357668424952</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3321171998977661</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7780572770844109</v>
+        <v>0.5237357748135897</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4499323070049286</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7780572850555053</v>
+        <v>0.5237357827846841</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3075082302093506</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7780572930265998</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3478826582431793</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2799999920000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7780572930265998</v>
+        <v>0.5237357907557786</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5586281418800354</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.279999972000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7780573328820721</v>
+        <v>0.5237358306112508</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5178598165512085</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.079999952000001</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.778057396650828</v>
+        <v>0.5237358943800067</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.519135057926178</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.279999972000001</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7780575082461504</v>
+        <v>0.5237360059753291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3743234574794769</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7780575560727171</v>
+        <v>0.5237360538018958</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4308228194713593</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7780575162172448</v>
+        <v>0.5237360139464236</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5164390206336975</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.2799999920000001</v>
+        <v>0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7780574444773947</v>
+        <v>0.5237359422065735</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.4043155014514923</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.2799999920000001</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7780575640438115</v>
+        <v>0.5237360617729903</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4242474734783173</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7780574046219224</v>
+        <v>0.5237359023511011</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.3938714563846588</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.778057173460183</v>
+        <v>0.5237356711893617</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4015948474407196</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7780571256336163</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3429473638534546</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7780571575179941</v>
+        <v>0.5237356552471728</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.40123251080513</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2829872667789459</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2948794662952423</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7780571415758052</v>
+        <v>0.5237356393049839</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3098740875720978</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7780570220093881</v>
+        <v>0.5237355197385668</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.3999412655830383</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7780569821539158</v>
+        <v>0.5237354798830945</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4385546147823334</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7780571256336163</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.3790748417377472</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.778057261142222</v>
+        <v>0.5237357588714008</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2739780247211456</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7780572452000331</v>
+        <v>0.5237357429292118</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.328715980052948</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3176895081996918</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5199999880000002</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7780571814312774</v>
+        <v>0.5237356791604562</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3577377498149872</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.4799999920000002</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7780570778070495</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5572539567947388</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7780569582406325</v>
+        <v>0.5237354559698112</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3547311425209045</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.4799999920000002</v>
+        <v>0.16</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7780570778070495</v>
+        <v>0.5237355755362283</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4678047299385071</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3199999880000002</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7780571256336163</v>
+        <v>0.523735623362795</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.2977302968502045</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3199999880000002</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7780572212867497</v>
+        <v>0.5237357190159284</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3629263937473297</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7780571017203328</v>
+        <v>0.5237355994495116</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4731442034244537</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5199999880000002</v>
+        <v>0.02000000000000013</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7780571096914273</v>
+        <v>0.5237356074206061</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_1_000001.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000001.xlsx
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.508387565612793</v>
+        <v>0.5083875060081482</v>
       </c>
       <c r="JB17" t="n">
         <v>0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3555789887905121</v>
+        <v>0.3555789589881897</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.208074077963829</v>
+        <v>0.2080740928649902</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.5558707714080811</v>
+        <v>0.5558707118034363</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.3</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4811369478702545</v>
+        <v>0.4811368882656097</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.4661517739295959</v>
+        <v>0.4661518037319183</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0.5237360697440847</v>
@@ -55799,7 +55799,7 @@
         <v>0.4287459254264832</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0.5237358226401564</v>
@@ -56594,7 +56594,7 @@
         <v>0.4971959292888641</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0.5237357827846841</v>
@@ -57389,7 +57389,7 @@
         <v>0.4362983107566833</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0.5237357190159284</v>
@@ -58184,7 +58184,7 @@
         <v>0.4070096909999847</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0.5237357907557786</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.3848070502281189</v>
+        <v>0.3848069906234741</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.306883305311203</v>
+        <v>0.3068832755088806</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.3478826582431793</v>
+        <v>0.3478826880455017</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.5178598165512085</v>
+        <v>0.5178598761558533</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.3429473638534546</v>
+        <v>0.3429474234580994</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.2829872667789459</v>
+        <v>0.2829872965812683</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.4385546147823334</v>
+        <v>0.4385546743869781</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2739780247211456</v>
+        <v>0.2739780843257904</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.1199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.328715980052948</v>
+        <v>0.3287160098552704</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.3999999999999999</v>
